--- a/vault-dalarna-university/01 IIT/Analys/Stavfel och språkbruk.xlsx
+++ b/vault-dalarna-university/01 IIT/Analys/Stavfel och språkbruk.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Stavfel och språkbruk" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$70</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -499,7 +499,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>BY1047</t>
+          <t>BY1065</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,24 +509,24 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>`buildingprocess` (en)</t>
+          <t>`connectmöten` (sv)</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BY1047</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BY1065</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>BY1047</t>
+          <t>BY2016</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -541,19 +541,19 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>`competion` (en)</t>
+          <t>`knowledges` (en)</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BY1047</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BY2016</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>BY1047</t>
+          <t>BY2016</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -568,51 +568,51 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>`shouldbe` (en)</t>
+          <t>`standars` (en)</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BY1047</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BY2016</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>BFY224</t>
+          <t>BY2016</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>FYA</t>
+          <t>BYA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>`preparandnivå` (sv)</t>
+          <t>`xxxxx` (en)</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BFY224</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BY2016</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>BFY225</t>
+          <t>BY3005</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>FYA</t>
+          <t>BYA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -622,24 +622,24 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>`fup` (en)</t>
+          <t>`neighbourhood` (en)</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BFY225</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BY3005</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>BFY226</t>
+          <t>BY3005</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>FYA</t>
+          <t>BYA</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -649,105 +649,105 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>`fup` (en)</t>
+          <t>`neighbourhoods` (en)</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BFY226</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BY3005</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>BFY227</t>
+          <t>GBY34B</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>FYA</t>
+          <t>BYA</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>`fup` (en)</t>
+          <t>`tillämningar` (sv)</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BFY227</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY34B</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>AIK232</t>
+          <t>GBY34B</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>BYA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>`immon` (en)</t>
+          <t>`vägprojekteringshjälpmedel` (sv)</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AIK232</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY34B</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>GIK29B</t>
+          <t>BFY224</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>FYA</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>`vgs` (en)</t>
+          <t>`preparandnivå` (sv)</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK29B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BFY224</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>GMA2EY</t>
+          <t>BFY225</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>MAA</t>
+          <t>FYA</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -757,105 +757,105 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>`indicies` (en)</t>
+          <t>`fup` (en)</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMA2EY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BFY225</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>MA0011</t>
+          <t>BFY226</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>MAA</t>
+          <t>FYA</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>`preparandnivå` (sv)</t>
+          <t>`fup` (en)</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MA0011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BFY226</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>MA0013</t>
+          <t>BFY227</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MAA</t>
+          <t>FYA</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>`preparandnivå` (sv)</t>
+          <t>`fup` (en)</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MA0013</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BFY227</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>GMD2PA</t>
+          <t>GIE3JW</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>IEA</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>`exeptions` (en)</t>
+          <t>`affärsplanbedömningar` (sv)</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2PA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE3JW</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>GMT34K</t>
+          <t>AIK232</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -865,24 +865,24 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>`programing` (en)</t>
+          <t>`immon` (en)</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT34K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AIK232</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>GMT34R</t>
+          <t>GIK29B</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -892,24 +892,24 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>`variousengineering` (en)</t>
+          <t>`vgs` (en)</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT34R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK29B</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>AEG2AL</t>
+          <t>GMA2EY</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MAA</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -919,186 +919,186 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>`andrelate` (en)</t>
+          <t>`indicies` (en)</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2AL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMA2EY</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>AEG2AQ</t>
+          <t>MA0011</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MAA</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>`adress` (en)</t>
+          <t>`preparandnivå` (sv)</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2AQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MA0011</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>AEG2C5</t>
+          <t>MA0013</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MAA</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>`laboatory` (en)</t>
+          <t>`preparandnivå` (sv)</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2C5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MA0013</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>EG3014</t>
+          <t>MA1042</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MAA</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>`appropiate` (en)</t>
+          <t>`reellvärda` (sv)</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3014</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MA1042</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>EG3014</t>
+          <t>MD1085</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>`crediits` (en)</t>
+          <t>`förutsättingar` (sv)</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3014</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1085</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>GEG2ZR</t>
+          <t>MD1097</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>`inlämingsuppgifter` (sv)</t>
+          <t>`babylonian` (en)</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG2ZR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1097</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>GSQ33N</t>
+          <t>MD1097</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SQQ</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>`skalniåver` (sv)</t>
+          <t>`mayan` (en)</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ33N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1097</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>GMI23G</t>
+          <t>MD1097</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1108,24 +1108,24 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>`eulides` (en)</t>
+          <t>`sumerian` (en)</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI23G</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1097</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>GMI2C8</t>
+          <t>MD1098</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1135,71 +1135,1205 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>`credtis` (en)</t>
+          <t>`pupls` (en)</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI2C8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1098</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>GMI2C8</t>
+          <t>GMT25Z</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>`mathodology` (en)</t>
+          <t>`avstämmningar` (sv)</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI2C8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT25Z</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>GMT25Z</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>MTA</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>`startgodkännandeformulär` (sv)</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT25Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>GMT25Z</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>MTA</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>`minumum` (en)</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT25Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>GMT2QF</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>MTA</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>`reults` (en)</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT2QF</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>GMT34K</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>MTA</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>`programing` (en)</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT34K</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>GMT34R</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>MTA</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>`variousengineering` (en)</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT34R</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>GMT3JQ</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>MTA</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>`mechatronic` (en)</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT3JQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>GMT3JT</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>MTA</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>`eu-förordningen` (sv)</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT3JT</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>GMT3JV</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>MTA</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>`cobots` (en)</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT3JV</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>MT1060</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>MTA</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>`böjmotstånd` (sv)</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT1060</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>MT1060</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>MTA</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>`vridspänningar` (sv)</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT1060</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>MT2006</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>MTA</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>`höckerlind` (sv)</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT2006</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>AEG225</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>`produktionskattelättnader` (sv)</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG225</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>AEG225</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>`softlån` (sv)</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG225</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>AEG22R</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>`mättteknik` (sv)</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG22R</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>AEG2AL</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>`andrelate` (en)</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2AL</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>AEG2AQ</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>`adress` (en)</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2AQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>AEG2AW</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>`wich` (en)</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2AW</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>AEG2AY</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>`inlämninguppgifter` (sv)</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2AY</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>AEG2C5</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>`laboatory` (en)</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2C5</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>EG3007</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>`absorbers` (en)</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3007</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>EG3012</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>`bioenergy` (en)</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3012</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>EG3012</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>`biofuel` (en)</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3012</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>EG3014</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>`appropiate` (en)</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3014</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>EG3014</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>`crediits` (en)</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3014</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>EG3015</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>`horizontoscope` (en)</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3015</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>EG3017</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>`genomförds` (sv)</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3017</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>EG3018</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>`genomförds` (sv)</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3018</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>EG4001</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>`continuewith` (en)</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG4001</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>EG4001</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>`fulltime` (en)</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG4001</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>EG4001</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>`insolation` (en)</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG4001</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>GEG26J</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>`tutoria` (en)</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG26J</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>GEG2UL</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>`microsystems` (en)</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG2UL</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>GEG2ZQ</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>`inlämninguppgifter` (sv)</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG2ZQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>GEG2ZQ</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>`solcellsanläggingar` (sv)</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG2ZQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>GEG2ZQ</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>`solstrålsberäkningar` (sv)</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG2ZQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>GEG2ZR</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>`inlämingsuppgifter` (sv)</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG2ZR</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>GSQ25J</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>SQQ</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Dubblerat ord</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>`hp` — …ch skriftliga inlämningsuppgifter i kvantitativa metoder, 4 hp hp  ## Arbetsformer  Föreläsningar, seminarier och övningar.…</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ25J</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>GSQ25K</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>SQQ</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>`gis-övningar` (sv)</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ25K</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>GSQ25K</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>SQQ</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>`skalniåver` (sv)</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ25K</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>GSQ33N</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>SQQ</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>`skalniåver` (sv)</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ33N</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>GMI23G</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>`eulides` (en)</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI23G</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>GMI2C8</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>`mathodology` (en)</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI2C8</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
           <t>GMI2J3</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B70" t="inlineStr">
         <is>
           <t>XYZ</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
         <is>
           <t>`discusess` (en)</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI2J3</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E28"/>
+  <autoFilter ref="A1:E70"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -1255,6 +2389,90 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId52"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A28" r:id="rId53"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A29" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A30" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A31" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A32" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A33" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A34" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A35" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A36" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A37" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A38" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A39" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A40" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A41" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A42" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A43" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A44" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A45" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A46" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A47" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A48" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A49" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A50" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A51" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A52" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A53" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A54" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A55" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A56" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E56" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A57" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E57" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A58" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E58" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A59" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E59" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A60" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E60" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A61" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E61" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A62" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E62" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A63" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A64" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A65" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E65" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A66" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E66" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A67" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E67" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A68" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E68" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A69" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E69" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A70" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E70" r:id="rId138"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/01 IIT/Analys/Stavfel och språkbruk.xlsx
+++ b/vault-dalarna-university/01 IIT/Analys/Stavfel och språkbruk.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Stavfel och språkbruk" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stavfel och språkbruk" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$67</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E70"/>
+  <dimension ref="A1:E67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -715,7 +715,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>BFY224</t>
+          <t>BFY225</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -725,24 +725,24 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>`preparandnivå` (sv)</t>
+          <t>`fup` (en)</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BFY224</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BFY225</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>BFY225</t>
+          <t>BFY226</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -762,14 +762,14 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BFY225</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BFY226</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>BFY226</t>
+          <t>BFY227</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -789,68 +789,68 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BFY226</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BFY227</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>BFY227</t>
+          <t>GIE3JW</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>FYA</t>
+          <t>IEA</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>`fup` (en)</t>
+          <t>`affärsplanbedömningar` (sv)</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BFY227</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE3JW</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>GIE3JW</t>
+          <t>AIK232</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>IEA</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>`affärsplanbedömningar` (sv)</t>
+          <t>`immon` (en)</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE3JW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AIK232</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>AIK232</t>
+          <t>GIK29B</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -865,24 +865,24 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>`immon` (en)</t>
+          <t>`vgs` (en)</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AIK232</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK29B</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>GIK29B</t>
+          <t>GMA2EY</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>MAA</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -892,19 +892,19 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>`vgs` (en)</t>
+          <t>`indicies` (en)</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK29B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMA2EY</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>GMA2EY</t>
+          <t>MA1042</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -914,29 +914,29 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>`indicies` (en)</t>
+          <t>`reellvärda` (sv)</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMA2EY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MA1042</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>MA0011</t>
+          <t>MD1085</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MAA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -946,73 +946,73 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>`preparandnivå` (sv)</t>
+          <t>`förutsättingar` (sv)</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MA0011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1085</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>MA0013</t>
+          <t>MD1097</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MAA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>`preparandnivå` (sv)</t>
+          <t>`babylonian` (en)</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MA0013</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1097</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>MA1042</t>
+          <t>MD1097</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MAA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>`reellvärda` (sv)</t>
+          <t>`mayan` (en)</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MA1042</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1097</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>MD1085</t>
+          <t>MD1097</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1022,24 +1022,24 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>`förutsättingar` (sv)</t>
+          <t>`sumerian` (en)</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1085</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1097</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>MD1097</t>
+          <t>MD1098</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1054,78 +1054,78 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>`babylonian` (en)</t>
+          <t>`pupls` (en)</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1097</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1098</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>MD1097</t>
+          <t>GMT25Z</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>`mayan` (en)</t>
+          <t>`avstämmningar` (sv)</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1097</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT25Z</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>MD1097</t>
+          <t>GMT25Z</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>`sumerian` (en)</t>
+          <t>`startgodkännandeformulär` (sv)</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1097</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT25Z</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>MD1098</t>
+          <t>GMT25Z</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1135,19 +1135,19 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>`pupls` (en)</t>
+          <t>`minumum` (en)</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1098</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT25Z</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>GMT25Z</t>
+          <t>GMT2QF</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1157,24 +1157,24 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>`avstämmningar` (sv)</t>
+          <t>`reults` (en)</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT25Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT2QF</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>GMT25Z</t>
+          <t>GMT34K</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1184,24 +1184,24 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>`startgodkännandeformulär` (sv)</t>
+          <t>`programing` (en)</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT25Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT34K</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>GMT25Z</t>
+          <t>GMT34R</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1216,19 +1216,19 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>`minumum` (en)</t>
+          <t>`variousengineering` (en)</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT25Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT34R</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>GMT2QF</t>
+          <t>GMT3JQ</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1243,19 +1243,19 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>`reults` (en)</t>
+          <t>`mechatronic` (en)</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT2QF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT3JQ</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>GMT34K</t>
+          <t>GMT3JT</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1265,24 +1265,24 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>`programing` (en)</t>
+          <t>`eu-förordningen` (sv)</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT34K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT3JT</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>GMT34R</t>
+          <t>GMT3JV</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1297,19 +1297,19 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>`variousengineering` (en)</t>
+          <t>`cobots` (en)</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT34R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT3JV</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>GMT3JQ</t>
+          <t>MT1060</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1319,24 +1319,24 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>`mechatronic` (en)</t>
+          <t>`böjmotstånd` (sv)</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT3JQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT1060</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>GMT3JT</t>
+          <t>MT1060</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1351,19 +1351,19 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>`eu-förordningen` (sv)</t>
+          <t>`vridspänningar` (sv)</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT3JT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT1060</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>GMT3JV</t>
+          <t>MT2006</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1373,29 +1373,29 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>`cobots` (en)</t>
+          <t>`höckerlind` (sv)</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT3JV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT2006</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>MT1060</t>
+          <t>AEG225</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1405,24 +1405,24 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>`böjmotstånd` (sv)</t>
+          <t>`produktionskattelättnader` (sv)</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT1060</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG225</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>MT1060</t>
+          <t>AEG225</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1432,24 +1432,24 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>`vridspänningar` (sv)</t>
+          <t>`softlån` (sv)</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT1060</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG225</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>MT2006</t>
+          <t>AEG22R</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1459,19 +1459,19 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>`höckerlind` (sv)</t>
+          <t>`mättteknik` (sv)</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT2006</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG22R</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>AEG225</t>
+          <t>AEG2AL</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1481,24 +1481,24 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>`produktionskattelättnader` (sv)</t>
+          <t>`andrelate` (en)</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG225</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2AL</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>AEG225</t>
+          <t>AEG2AQ</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1508,24 +1508,24 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>`softlån` (sv)</t>
+          <t>`adress` (en)</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG225</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2AQ</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>AEG22R</t>
+          <t>AEG2AW</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1535,24 +1535,24 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>`mättteknik` (sv)</t>
+          <t>`wich` (en)</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG22R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2AW</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>AEG2AL</t>
+          <t>AEG2AY</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1562,24 +1562,24 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>`andrelate` (en)</t>
+          <t>`inlämninguppgifter` (sv)</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2AL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2AY</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>AEG2AQ</t>
+          <t>AEG2C5</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1594,19 +1594,19 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>`adress` (en)</t>
+          <t>`laboatory` (en)</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2AQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2C5</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>AEG2AW</t>
+          <t>EG3007</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1621,19 +1621,19 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>`wich` (en)</t>
+          <t>`absorbers` (en)</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2AW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3007</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>AEG2AY</t>
+          <t>EG3012</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1643,24 +1643,24 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>`inlämninguppgifter` (sv)</t>
+          <t>`bioenergy` (en)</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2AY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3012</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>AEG2C5</t>
+          <t>EG3012</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1675,19 +1675,19 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>`laboatory` (en)</t>
+          <t>`biofuel` (en)</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2C5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3012</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>EG3007</t>
+          <t>EG3014</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1702,19 +1702,19 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>`absorbers` (en)</t>
+          <t>`appropiate` (en)</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3014</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>EG3012</t>
+          <t>EG3014</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1729,19 +1729,19 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>`bioenergy` (en)</t>
+          <t>`crediits` (en)</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3014</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>EG3012</t>
+          <t>EG3015</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1756,19 +1756,19 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>`biofuel` (en)</t>
+          <t>`horizontoscope` (en)</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3015</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>EG3014</t>
+          <t>EG3017</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1778,24 +1778,24 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>`appropiate` (en)</t>
+          <t>`genomförds` (sv)</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3014</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3017</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>EG3014</t>
+          <t>EG3018</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1805,24 +1805,24 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>`crediits` (en)</t>
+          <t>`genomförds` (sv)</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3014</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3018</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>EG3015</t>
+          <t>EG4001</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1837,19 +1837,19 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>`horizontoscope` (en)</t>
+          <t>`continuewith` (en)</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG4001</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>EG3017</t>
+          <t>EG4001</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1859,24 +1859,24 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>`genomförds` (sv)</t>
+          <t>`fulltime` (en)</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3017</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG4001</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>EG3018</t>
+          <t>EG4001</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1886,24 +1886,24 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>`genomförds` (sv)</t>
+          <t>`insolation` (en)</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3018</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG4001</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>EG4001</t>
+          <t>GEG26J</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1918,19 +1918,19 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>`continuewith` (en)</t>
+          <t>`tutoria` (en)</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG4001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG26J</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>EG4001</t>
+          <t>GEG2UL</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1945,19 +1945,19 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>`fulltime` (en)</t>
+          <t>`microsystems` (en)</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG4001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG2UL</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>EG4001</t>
+          <t>GEG2ZQ</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1967,24 +1967,24 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>`insolation` (en)</t>
+          <t>`inlämninguppgifter` (sv)</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG4001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG2ZQ</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>GEG26J</t>
+          <t>GEG2ZQ</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1994,24 +1994,24 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>`tutoria` (en)</t>
+          <t>`solcellsanläggingar` (sv)</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG26J</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG2ZQ</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>GEG2UL</t>
+          <t>GEG2ZQ</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2021,24 +2021,24 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>`microsystems` (en)</t>
+          <t>`solstrålsberäkningar` (sv)</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG2UL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG2ZQ</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>GEG2ZQ</t>
+          <t>GEG2ZR</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2053,51 +2053,51 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>`inlämninguppgifter` (sv)</t>
+          <t>`inlämingsuppgifter` (sv)</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG2ZQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG2ZR</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>GEG2ZQ</t>
+          <t>GSQ25J</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>SQQ</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>`solcellsanläggingar` (sv)</t>
+          <t>`hp` — …ch skriftliga inlämningsuppgifter i kvantitativa metoder, 4 hp hp  ## Arbetsformer  Föreläsningar, seminarier och övningar.…</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG2ZQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ25J</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>GEG2ZQ</t>
+          <t>GSQ25K</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>SQQ</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2107,24 +2107,24 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>`solstrålsberäkningar` (sv)</t>
+          <t>`gis-övningar` (sv)</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG2ZQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ25K</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>GEG2ZR</t>
+          <t>GSQ25K</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>SQQ</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2134,19 +2134,19 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>`inlämingsuppgifter` (sv)</t>
+          <t>`skalniåver` (sv)</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG2ZR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ25K</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>GSQ25J</t>
+          <t>GSQ33N</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2156,184 +2156,103 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Dubblerat ord</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>`hp` — …ch skriftliga inlämningsuppgifter i kvantitativa metoder, 4 hp hp  ## Arbetsformer  Föreläsningar, seminarier och övningar.…</t>
+          <t>`skalniåver` (sv)</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ25J</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ33N</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>GSQ25K</t>
+          <t>GMI23G</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>SQQ</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>`gis-övningar` (sv)</t>
+          <t>`eulides` (en)</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ25K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI23G</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>GSQ25K</t>
+          <t>GMI2C8</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>SQQ</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>`skalniåver` (sv)</t>
+          <t>`mathodology` (en)</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ25K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI2C8</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>GSQ33N</t>
+          <t>GMI2J3</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>SQQ</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>`skalniåver` (sv)</t>
+          <t>`discusess` (en)</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ33N</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>GMI23G</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>XYZ</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>`eulides` (en)</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI23G</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>GMI2C8</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>XYZ</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>`mathodology` (en)</t>
-        </is>
-      </c>
-      <c r="E69" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI2C8</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>GMI2J3</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>XYZ</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>`discusess` (en)</t>
-        </is>
-      </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI2J3</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E70"/>
+  <autoFilter ref="A1:E67"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -2467,12 +2386,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E66" r:id="rId130"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A67" r:id="rId131"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E67" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A68" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E68" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A69" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E69" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A70" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E70" r:id="rId138"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/01 IIT/Analys/Stavfel och språkbruk.xlsx
+++ b/vault-dalarna-university/01 IIT/Analys/Stavfel och språkbruk.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stavfel och språkbruk" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Stavfel och språkbruk" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$67</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$53</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E67"/>
+  <dimension ref="A1:E53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -499,7 +499,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>BY1065</t>
+          <t>BY2016</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,17 +509,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>`connectmöten` (sv)</t>
+          <t>`knowledges` (en)</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BY1065</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BY2016</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>`knowledges` (en)</t>
+          <t>`standars` (en)</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>`standars` (en)</t>
+          <t>`xxxxx` (en)</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -580,7 +580,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>BY2016</t>
+          <t>GBY34B</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -590,29 +590,29 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>`xxxxx` (en)</t>
+          <t>`tillämningar` (sv)</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BY2016</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY34B</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>BY3005</t>
+          <t>BFY225</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BYA</t>
+          <t>FYA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -622,24 +622,24 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>`neighbourhood` (en)</t>
+          <t>`fup` (en)</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BY3005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BFY225</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>BY3005</t>
+          <t>BFY226</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BYA</t>
+          <t>FYA</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -649,78 +649,78 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>`neighbourhoods` (en)</t>
+          <t>`fup` (en)</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BY3005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BFY226</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>GBY34B</t>
+          <t>BFY227</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BYA</t>
+          <t>FYA</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>`tillämningar` (sv)</t>
+          <t>`fup` (en)</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY34B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BFY227</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>GBY34B</t>
+          <t>AIK232</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BYA</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>`vägprojekteringshjälpmedel` (sv)</t>
+          <t>`immon` (en)</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY34B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AIK232</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>BFY225</t>
+          <t>GIK29B</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>FYA</t>
+          <t>IKA</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -730,24 +730,24 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>`fup` (en)</t>
+          <t>`vgs` (en)</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BFY225</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK29B</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>BFY226</t>
+          <t>GMA2EY</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>FYA</t>
+          <t>MAA</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -757,213 +757,213 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>`fup` (en)</t>
+          <t>`indicies` (en)</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BFY226</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMA2EY</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>BFY227</t>
+          <t>MD1085</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>FYA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>`fup` (en)</t>
+          <t>`förutsättingar` (sv)</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BFY227</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1085</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>GIE3JW</t>
+          <t>MD1098</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>IEA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>`affärsplanbedömningar` (sv)</t>
+          <t>`pupls` (en)</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE3JW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1098</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>AIK232</t>
+          <t>GMT25Z</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>`immon` (en)</t>
+          <t>`avstämmning` → avstämning</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AIK232</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT25Z</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>GIK29B</t>
+          <t>GMT25Z</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>IKA</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>`vgs` (en)</t>
+          <t>`avstämmningar` (sv)</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK29B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT25Z</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>GMA2EY</t>
+          <t>GMT25Z</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>MAA</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>`indicies` (en)</t>
+          <t>`startgodkännandeformulär` (sv)</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMA2EY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT25Z</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>MA1042</t>
+          <t>GMT25Z</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MAA</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>`reellvärda` (sv)</t>
+          <t>`minumum` (en)</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MA1042</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT25Z</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>MD1085</t>
+          <t>GMT2QF</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>`förutsättingar` (sv)</t>
+          <t>`reults` (en)</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1085</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT2QF</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>MD1097</t>
+          <t>GMT34K</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -973,24 +973,24 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>`babylonian` (en)</t>
+          <t>`programing` (en)</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1097</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT34K</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>MD1097</t>
+          <t>GMT34R</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1000,24 +1000,24 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>`mayan` (en)</t>
+          <t>`variousengineering` (en)</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1097</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT34R</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>MD1097</t>
+          <t>GMT3JQ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1027,46 +1027,46 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>`sumerian` (en)</t>
+          <t>`mechatronic` (en)</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1097</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT3JQ</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>MD1098</t>
+          <t>GMT3JT</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>`pupls` (en)</t>
+          <t>`eu-förordningen` (sv)</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1098</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT3JT</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>GMT25Z</t>
+          <t>MT1060</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1081,19 +1081,19 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>`avstämmningar` (sv)</t>
+          <t>`vridspänningar` (sv)</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT25Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT1060</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>GMT25Z</t>
+          <t>MT2006</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1108,105 +1108,105 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>`startgodkännandeformulär` (sv)</t>
+          <t>`höckerlind` (sv)</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT25Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT2006</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>GMT25Z</t>
+          <t>AEG225</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>`minumum` (en)</t>
+          <t>`produktionskattelättnader` (sv)</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT25Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG225</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>GMT2QF</t>
+          <t>AEG225</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>`reults` (en)</t>
+          <t>`softlån` (sv)</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT2QF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG225</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>GMT34K</t>
+          <t>AEG22R</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>`programing` (en)</t>
+          <t>`mättteknik` (sv)</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT34K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG22R</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>GMT34R</t>
+          <t>AEG2AL</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1216,24 +1216,24 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>`variousengineering` (en)</t>
+          <t>`andrelate` (en)</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT34R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2AL</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>GMT3JQ</t>
+          <t>AEG2AQ</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1243,154 +1243,154 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>`mechatronic` (en)</t>
+          <t>`adress` (en)</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT3JQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2AQ</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>GMT3JT</t>
+          <t>AEG2AW</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>`eu-förordningen` (sv)</t>
+          <t>`wich` (en)</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT3JT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2AW</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>GMT3JV</t>
+          <t>AEG2AY</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>`cobots` (en)</t>
+          <t>`inlämninguppgifter` (sv)</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT3JV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2AY</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>MT1060</t>
+          <t>AEG2C5</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>`böjmotstånd` (sv)</t>
+          <t>`laboatory` (en)</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT1060</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2C5</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>MT1060</t>
+          <t>EG3007</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>`vridspänningar` (sv)</t>
+          <t>`absorbers` (en)</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT1060</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3007</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>MT2006</t>
+          <t>EG3014</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>`höckerlind` (sv)</t>
+          <t>`appropiate` (en)</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT2006</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3014</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>AEG225</t>
+          <t>EG3014</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1400,24 +1400,24 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>`produktionskattelättnader` (sv)</t>
+          <t>`crediits` (en)</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG225</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3014</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>AEG225</t>
+          <t>EG3015</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1427,24 +1427,24 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>`softlån` (sv)</t>
+          <t>`horizontoscope` (en)</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG225</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3015</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>AEG22R</t>
+          <t>EG3017</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1459,19 +1459,19 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>`mättteknik` (sv)</t>
+          <t>`genomförds` (sv)</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG22R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3017</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>AEG2AL</t>
+          <t>EG3018</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1481,24 +1481,24 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>`andrelate` (en)</t>
+          <t>`genomförds` (sv)</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2AL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3018</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>AEG2AQ</t>
+          <t>EG4001</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1513,19 +1513,19 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>`adress` (en)</t>
+          <t>`continuewith` (en)</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2AQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG4001</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>AEG2AW</t>
+          <t>EG4001</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1540,19 +1540,19 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>`wich` (en)</t>
+          <t>`fulltime` (en)</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2AW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG4001</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>AEG2AY</t>
+          <t>GEG26J</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1562,24 +1562,24 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>`inlämninguppgifter` (sv)</t>
+          <t>`tutoria` (en)</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2AY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG26J</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>AEG2C5</t>
+          <t>GEG2ZQ</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1589,24 +1589,24 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>`laboatory` (en)</t>
+          <t>`inlämninguppgifter` (sv)</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2C5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG2ZQ</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>EG3007</t>
+          <t>GEG2ZQ</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>`absorbers` (en)</t>
+          <t>`solcellsanläggingar` (sv)</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG2ZQ</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>EG3012</t>
+          <t>GEG2ZQ</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1643,24 +1643,24 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>`bioenergy` (en)</t>
+          <t>`solstrålsberäkningar` (sv)</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG2ZQ</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>EG3012</t>
+          <t>GEG2ZR</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1670,110 +1670,110 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>`biofuel` (en)</t>
+          <t>`inlämingsuppgifter` (sv)</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG2ZR</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>EG3014</t>
+          <t>GSQ25J</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>SQQ</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>`appropiate` (en)</t>
+          <t>`hp` — …ch skriftliga inlämningsuppgifter i kvantitativa metoder, 4 hp hp  ## Arbetsformer  Föreläsningar, seminarier och övningar.…</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3014</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ25J</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>EG3014</t>
+          <t>GSQ25K</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>SQQ</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>`crediits` (en)</t>
+          <t>`gis-övningar` (sv)</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3014</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ25K</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>EG3015</t>
+          <t>GSQ25K</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>SQQ</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>`horizontoscope` (en)</t>
+          <t>`skalniåver` (sv)</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ25K</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>EG3017</t>
+          <t>GSQ33N</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>SQQ</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1783,51 +1783,51 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>`genomförds` (sv)</t>
+          <t>`skalniåver` (sv)</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3017</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ33N</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>EG3018</t>
+          <t>GMI23G</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>`genomförds` (sv)</t>
+          <t>`eulides` (en)</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3018</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI23G</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>EG4001</t>
+          <t>GMI2C8</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1837,24 +1837,24 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>`continuewith` (en)</t>
+          <t>`mathodology` (en)</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG4001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI2C8</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>EG4001</t>
+          <t>GMI2J3</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1864,395 +1864,17 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>`fulltime` (en)</t>
+          <t>`discusess` (en)</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG4001</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>EG4001</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>MÖY</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>`insolation` (en)</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG4001</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>GEG26J</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>MÖY</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>`tutoria` (en)</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG26J</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>GEG2UL</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>MÖY</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>`microsystems` (en)</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG2UL</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>GEG2ZQ</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>MÖY</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>`inlämninguppgifter` (sv)</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG2ZQ</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>GEG2ZQ</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>MÖY</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>`solcellsanläggingar` (sv)</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG2ZQ</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>GEG2ZQ</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>MÖY</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>`solstrålsberäkningar` (sv)</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG2ZQ</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>GEG2ZR</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>MÖY</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>`inlämingsuppgifter` (sv)</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG2ZR</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>GSQ25J</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>SQQ</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Dubblerat ord</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>`hp` — …ch skriftliga inlämningsuppgifter i kvantitativa metoder, 4 hp hp  ## Arbetsformer  Föreläsningar, seminarier och övningar.…</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ25J</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>GSQ25K</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>SQQ</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>`gis-övningar` (sv)</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ25K</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>GSQ25K</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>SQQ</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>`skalniåver` (sv)</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ25K</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>GSQ33N</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>SQQ</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>`skalniåver` (sv)</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ33N</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>GMI23G</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>XYZ</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>`eulides` (en)</t>
-        </is>
-      </c>
-      <c r="E65" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI23G</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>GMI2C8</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>XYZ</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>`mathodology` (en)</t>
-        </is>
-      </c>
-      <c r="E66" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI2C8</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>GMI2J3</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>XYZ</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>`discusess` (en)</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI2J3</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E67"/>
+  <autoFilter ref="A1:E53"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -2358,34 +1980,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId102"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A53" r:id="rId103"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A54" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A55" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A56" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E56" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A57" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E57" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A58" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E58" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A59" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E59" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A60" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E60" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A61" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E61" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A62" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E62" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A63" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A64" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A65" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E65" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A66" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E66" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A67" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E67" r:id="rId132"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/01 IIT/Analys/Stavfel och språkbruk.xlsx
+++ b/vault-dalarna-university/01 IIT/Analys/Stavfel och språkbruk.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Stavfel och språkbruk" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$46</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E53"/>
+  <dimension ref="A1:E46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1039,12 +1039,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>GMT3JT</t>
+          <t>AEG225</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1054,24 +1054,24 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>`eu-förordningen` (sv)</t>
+          <t>`produktionskattelättnader` (sv)</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT3JT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG225</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>MT1060</t>
+          <t>AEG22R</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1081,46 +1081,46 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>`vridspänningar` (sv)</t>
+          <t>`mättteknik` (sv)</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT1060</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG22R</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>MT2006</t>
+          <t>AEG2AL</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>`höckerlind` (sv)</t>
+          <t>`andrelate` (en)</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MT2006</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2AL</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>AEG225</t>
+          <t>AEG2AQ</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1130,24 +1130,24 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>`produktionskattelättnader` (sv)</t>
+          <t>`adress` (en)</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG225</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2AQ</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>AEG225</t>
+          <t>AEG2AW</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1157,24 +1157,24 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>`softlån` (sv)</t>
+          <t>`wich` (en)</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG225</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2AW</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>AEG22R</t>
+          <t>AEG2AY</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1189,19 +1189,19 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>`mättteknik` (sv)</t>
+          <t>`inlämninguppgifter` (sv)</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG22R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2AY</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>AEG2AL</t>
+          <t>AEG2C5</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1216,19 +1216,19 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>`andrelate` (en)</t>
+          <t>`laboatory` (en)</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2AL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2C5</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>AEG2AQ</t>
+          <t>EG3007</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1243,19 +1243,19 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>`adress` (en)</t>
+          <t>`absorbers` (en)</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2AQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3007</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>AEG2AW</t>
+          <t>EG3014</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1270,19 +1270,19 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>`wich` (en)</t>
+          <t>`appropiate` (en)</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2AW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3014</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>AEG2AY</t>
+          <t>EG3014</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1292,24 +1292,24 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>`inlämninguppgifter` (sv)</t>
+          <t>`crediits` (en)</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2AY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3014</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>AEG2C5</t>
+          <t>EG3015</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1324,19 +1324,19 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>`laboatory` (en)</t>
+          <t>`horizontoscope` (en)</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2C5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3015</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>EG3007</t>
+          <t>EG3017</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1346,24 +1346,24 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>`absorbers` (en)</t>
+          <t>`genomförds` (sv)</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3017</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>EG3014</t>
+          <t>EG3018</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1373,24 +1373,24 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>`appropiate` (en)</t>
+          <t>`genomförds` (sv)</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3014</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3018</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>EG3014</t>
+          <t>EG4001</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1405,19 +1405,19 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>`crediits` (en)</t>
+          <t>`continuewith` (en)</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3014</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG4001</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>EG3015</t>
+          <t>EG4001</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1432,19 +1432,19 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>`horizontoscope` (en)</t>
+          <t>`fulltime` (en)</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG4001</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>EG3017</t>
+          <t>GEG26J</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1454,24 +1454,24 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>`genomförds` (sv)</t>
+          <t>`tutoria` (en)</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3017</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG26J</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>EG3018</t>
+          <t>GEG2ZQ</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1486,19 +1486,19 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>`genomförds` (sv)</t>
+          <t>`inlämninguppgifter` (sv)</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3018</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG2ZQ</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>EG4001</t>
+          <t>GEG2ZR</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1508,83 +1508,83 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>`continuewith` (en)</t>
+          <t>`inlämingsuppgifter` (sv)</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG4001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG2ZR</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>EG4001</t>
+          <t>GSQ25J</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>SQQ</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Dubblerat ord</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>`fulltime` (en)</t>
+          <t>`hp` — …ch skriftliga inlämningsuppgifter i kvantitativa metoder, 4 hp hp  ## Arbetsformer  Föreläsningar, seminarier och övningar.…</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG4001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ25J</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>GEG26J</t>
+          <t>GSQ25K</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>SQQ</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>`tutoria` (en)</t>
+          <t>`skalniåver` (sv)</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG26J</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ25K</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>GEG2ZQ</t>
+          <t>GSQ33N</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>SQQ</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1594,287 +1594,98 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>`inlämninguppgifter` (sv)</t>
+          <t>`skalniåver` (sv)</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG2ZQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ33N</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>GEG2ZQ</t>
+          <t>GMI23G</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>`solcellsanläggingar` (sv)</t>
+          <t>`eulides` (en)</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG2ZQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI23G</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>GEG2ZQ</t>
+          <t>GMI2C8</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>`solstrålsberäkningar` (sv)</t>
+          <t>`mathodology` (en)</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG2ZQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI2C8</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>GEG2ZR</t>
+          <t>GMI2J3</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>`inlämingsuppgifter` (sv)</t>
+          <t>`discusess` (en)</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG2ZR</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>GSQ25J</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>SQQ</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Dubblerat ord</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>`hp` — …ch skriftliga inlämningsuppgifter i kvantitativa metoder, 4 hp hp  ## Arbetsformer  Föreläsningar, seminarier och övningar.…</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ25J</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>GSQ25K</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>SQQ</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>`gis-övningar` (sv)</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ25K</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>GSQ25K</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>SQQ</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>`skalniåver` (sv)</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ25K</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>GSQ33N</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>SQQ</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>`skalniåver` (sv)</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ33N</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>GMI23G</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>XYZ</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>`eulides` (en)</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI23G</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>GMI2C8</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>XYZ</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>`mathodology` (en)</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI2C8</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>GMI2J3</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>XYZ</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>`discusess` (en)</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI2J3</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E53"/>
+  <autoFilter ref="A1:E46"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -1966,20 +1777,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId88"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A46" r:id="rId89"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A47" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A48" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A49" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A50" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A51" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A52" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A53" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId104"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/01 IIT/Analys/Stavfel och språkbruk.xlsx
+++ b/vault-dalarna-university/01 IIT/Analys/Stavfel och språkbruk.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>`indicies` (en)</t>
+          <t>`indicies` → indices (en)</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -769,34 +769,34 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>MD1085</t>
+          <t>GMA2EY</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>MDI</t>
+          <t>MAA</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>`förutsättingar` (sv)</t>
+          <t>`indicies` (en)</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1085</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMA2EY</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>MD1098</t>
+          <t>MD1085</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -806,44 +806,44 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>`pupls` (en)</t>
+          <t>`förutsättingar` (sv)</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1098</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1085</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>GMT25Z</t>
+          <t>MD1098</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>MDI</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>`avstämmning` → avstämning</t>
+          <t>`pupls` (en)</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT25Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1098</t>
         </is>
       </c>
     </row>
@@ -865,7 +865,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>`avstämmningar` (sv)</t>
+          <t>`avstämmning` → avstämning</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>`startgodkännandeformulär` (sv)</t>
+          <t>`avstämmningar` (sv)</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>`minumum` (en)</t>
+          <t>`startgodkännandeformulär` (sv)</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>GMT2QF</t>
+          <t>GMT25Z</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -946,19 +946,19 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>`reults` (en)</t>
+          <t>`minumum` (en)</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT2QF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT25Z</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>GMT34K</t>
+          <t>GMT2QF</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -973,19 +973,19 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>`programing` (en)</t>
+          <t>`reults` (en)</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT34K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT2QF</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>GMT34R</t>
+          <t>GMT34K</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1000,19 +1000,19 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>`variousengineering` (en)</t>
+          <t>`programing` (en)</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT34R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT34K</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>GMT3JQ</t>
+          <t>GMT34R</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>`mechatronic` (en)</t>
+          <t>`variousengineering` (en)</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT3JQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT34R</t>
         </is>
       </c>
     </row>
@@ -1228,7 +1228,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>EG3007</t>
+          <t>EG3014</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1243,12 +1243,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>`absorbers` (en)</t>
+          <t>`appropiate` (en)</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3014</t>
         </is>
       </c>
     </row>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>`appropiate` (en)</t>
+          <t>`crediits` (en)</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -1282,7 +1282,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>EG3014</t>
+          <t>EG3017</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1292,24 +1292,24 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>`crediits` (en)</t>
+          <t>`genomförds` (sv)</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3014</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3017</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>EG3015</t>
+          <t>EG3018</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1319,24 +1319,24 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>`horizontoscope` (en)</t>
+          <t>`genomförds` (sv)</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3018</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>EG3017</t>
+          <t>EG4001</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1346,24 +1346,24 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>`genomförds` (sv)</t>
+          <t>`continuewith` (en)</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3017</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG4001</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>EG3018</t>
+          <t>EG4001</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1373,24 +1373,24 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>`genomförds` (sv)</t>
+          <t>`fulltime` (en)</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3018</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG4001</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>EG4001</t>
+          <t>GEG26J</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1405,19 +1405,19 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>`continuewith` (en)</t>
+          <t>`tutoria` (en)</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG4001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG26J</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>EG4001</t>
+          <t>GEG2ZQ</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1427,24 +1427,24 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>`fulltime` (en)</t>
+          <t>`solcellsanläggingar` → solcellsanläggningar</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG4001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG2ZQ</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>GEG26J</t>
+          <t>GEG2ZQ</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1454,17 +1454,17 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>`tutoria` (en)</t>
+          <t>`inlämninguppgifter` (sv)</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG26J</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG2ZQ</t>
         </is>
       </c>
     </row>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>`inlämninguppgifter` (sv)</t>
+          <t>`solcellsanläggingar` (sv)</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">

--- a/vault-dalarna-university/01 IIT/Analys/Stavfel och språkbruk.xlsx
+++ b/vault-dalarna-university/01 IIT/Analys/Stavfel och språkbruk.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Stavfel och språkbruk" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$46</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -472,113 +472,1220 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>GMA2EY</t>
+          <t>ABY2BL</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MAA</t>
+          <t>BYA</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>`indicies` → indices (en)</t>
+          <t>`witten` (en)</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMA2EY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ABY2BL</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>GMT25Z</t>
+          <t>BY2016</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>BYA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>`avstämmning` → avstämning</t>
+          <t>`knowledges` (en)</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT25Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BY2016</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>GEG2ZQ</t>
+          <t>BY2016</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MÖY</t>
+          <t>BYA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>`solcellsanläggingar` → solcellsanläggningar</t>
+          <t>`standars` (en)</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG2ZQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BY2016</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>BY2016</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>BYA</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>`xxxxx` (en)</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BY2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>GBY34B</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>BYA</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>`tillämningar` (sv)</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY34B</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>BFY225</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>FYA</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>`fup` (en)</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BFY225</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>BFY226</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>FYA</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>`fup` (en)</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BFY226</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>BFY227</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>FYA</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>`fup` (en)</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BFY227</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>AIK232</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>IKA</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>`immon` (en)</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AIK232</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>GIK29B</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>IKA</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>`vgs` (en)</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK29B</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>GMA2EY</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>MAA</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>`indicies` → indices (en)</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMA2EY</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>GMA2EY</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>MAA</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>`indicies` (en)</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMA2EY</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>MD1085</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>MDI</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>`förutsättingar` (sv)</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1085</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>MD1098</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>MDI</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>`pupls` (en)</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1098</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>GMT25Z</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>MTA</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>`avstämmning` → avstämning</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT25Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>GMT25Z</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>MTA</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>`avstämmningar` (sv)</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT25Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>GMT25Z</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>MTA</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>`startgodkännandeformulär` (sv)</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT25Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>GMT25Z</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>MTA</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>`minumum` (en)</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT25Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>GMT2QF</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>MTA</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>`reults` (en)</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT2QF</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>GMT34K</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>MTA</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>`programing` (en)</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT34K</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>GMT34R</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>MTA</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>`variousengineering` (en)</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT34R</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>AEG225</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>`produktionskattelättnader` (sv)</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG225</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>AEG22R</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>`mättteknik` (sv)</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG22R</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>AEG2AL</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>`andrelate` (en)</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2AL</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>AEG2AQ</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>`adress` (en)</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2AQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>AEG2AW</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>`wich` (en)</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2AW</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>AEG2AY</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>`inlämninguppgifter` (sv)</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2AY</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>AEG2C5</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>`laboatory` (en)</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG2C5</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>EG3014</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>`appropiate` (en)</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3014</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>EG3014</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>`crediits` (en)</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3014</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>EG3017</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>`genomförds` (sv)</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3017</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>EG3018</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>`genomförds` (sv)</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3018</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>EG4001</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>`continuewith` (en)</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG4001</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>EG4001</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>`fulltime` (en)</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG4001</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>GEG26J</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>`tutoria` (en)</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG26J</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>GEG2ZQ</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>`solcellsanläggingar` → solcellsanläggningar</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG2ZQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>GEG2ZQ</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>`inlämninguppgifter` (sv)</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG2ZQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>GEG2ZQ</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>`solcellsanläggingar` (sv)</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG2ZQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>GEG2ZR</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>`inlämingsuppgifter` (sv)</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG2ZR</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
           <t>GSQ25J</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>SQQ</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>Dubblerat ord</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>`hp` — …ch skriftliga inlämningsuppgifter i kvantitativa metoder, 4 hp hp  ## Arbetsformer  Föreläsningar, seminarier och övningar.…</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ25J</t>
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>GSQ25K</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>SQQ</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>`skalniåver` (sv)</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ25K</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>GSQ33N</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>SQQ</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>`skalniåver` (sv)</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ33N</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>GMI23G</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>`eulides` (en)</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI23G</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>GMI2C8</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>`mathodology` (en)</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI2C8</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>GMI2J3</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>`discusess` (en)</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI2J3</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E5"/>
+  <autoFilter ref="A1:E46"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -588,6 +1695,88 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A21" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A23" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A24" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A25" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A26" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A27" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A28" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A29" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A30" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A31" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A32" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A33" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A34" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A35" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A36" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A37" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A38" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A39" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A40" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A41" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A42" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A43" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A44" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A45" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A46" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId90"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/01 IIT/Analys/Stavfel och språkbruk.xlsx
+++ b/vault-dalarna-university/01 IIT/Analys/Stavfel och språkbruk.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Stavfel och språkbruk" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -472,66 +472,66 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>BY2016</t>
+          <t>GMA2EY</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BYA</t>
+          <t>MAA</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>`knowledges` (en)</t>
+          <t>`indicies` → indices (en)</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BY2016</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMA2EY</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>BY2016</t>
+          <t>GEG2ZQ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BYA</t>
+          <t>MÖY</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>`xxxxx` (en)</t>
+          <t>`solcellsanläggingar` → solcellsanläggningar</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BY2016</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG2ZQ</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>BFY225</t>
+          <t>GMI2C8</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>FYA</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -541,368 +541,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>`fup` (en)</t>
+          <t>`mathodology` (en)</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BFY225</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>BFY226</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>FYA</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>`fup` (en)</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BFY226</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>BFY227</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>FYA</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>`fup` (en)</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BFY227</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>AIK232</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>IKA</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>`immon` (en)</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AIK232</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>GMA2EY</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>MAA</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>`indicies` → indices (en)</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMA2EY</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>GMA2EY</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>MAA</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>`indicies` (en)</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMA2EY</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>GMT25Z</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>MTA</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>`startgodkännandeformulär` (sv)</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT25Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>AEG225</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>MÖY</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>`produktionskattelättnader` (sv)</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG225</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>GEG2ZQ</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>MÖY</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>`solcellsanläggingar` → solcellsanläggningar</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG2ZQ</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>GEG2ZQ</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>MÖY</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>`solcellsanläggingar` (sv)</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG2ZQ</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>GSQ25K</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>SQQ</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>`skalnivåer` (sv)</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ25K</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>GSQ33N</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>SQQ</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>`skalnivåer` (sv)</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ33N</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>GMI23G</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>XYZ</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>`euclidian` (en)</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI23G</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>GMI2C8</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>XYZ</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>`mathodology` (en)</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI2C8</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E17"/>
+  <autoFilter ref="A1:E4"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -910,32 +559,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId32"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/01 IIT/Analys/Stavfel och språkbruk.xlsx
+++ b/vault-dalarna-university/01 IIT/Analys/Stavfel och språkbruk.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Stavfel och språkbruk" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -472,93 +472,35 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>GMA2EY</t>
+          <t>GSQ23K</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MAA</t>
+          <t>SQQ</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Felstavning</t>
+          <t>Felstavning (en)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>`indicies` → indices (en)</t>
+          <t>`credtis` (en)</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMA2EY</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>GEG2ZQ</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>MÖY</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>`solcellsanläggingar` → solcellsanläggningar</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG2ZQ</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>GMI2C8</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>XYZ</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>`mathodology` (en)</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMI2C8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ23K</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E4"/>
+  <autoFilter ref="A1:E2"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/01 IIT/Analys/Stavfel och språkbruk.xlsx
+++ b/vault-dalarna-university/01 IIT/Analys/Stavfel och språkbruk.xlsx
@@ -9,9 +9,7 @@
   <sheets>
     <sheet name="Stavfel och språkbruk" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$2</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -19,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,10 +28,6 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-    </font>
-    <font>
-      <color rgb="000563C1"/>
-      <u val="single"/>
     </font>
   </fonts>
   <fills count="3">
@@ -61,12 +55,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -432,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -469,39 +462,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>GSQ23K</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>SQQ</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>`credtis` (en)</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ23K</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E2"/>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/vault-dalarna-university/01 IIT/Analys/Stavfel och språkbruk.xlsx
+++ b/vault-dalarna-university/01 IIT/Analys/Stavfel och språkbruk.xlsx
@@ -9,7 +9,9 @@
   <sheets>
     <sheet name="Stavfel och språkbruk" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$2</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -17,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,6 +30,10 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <color rgb="000563C1"/>
+      <u val="single"/>
     </font>
   </fonts>
   <fills count="3">
@@ -55,11 +61,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -462,7 +469,39 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>GSQ23K</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>SQQ</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>`credtis` (en)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ23K</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:E2"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/vault-dalarna-university/01 IIT/Analys/Stavfel och språkbruk.xlsx
+++ b/vault-dalarna-university/01 IIT/Analys/Stavfel och språkbruk.xlsx
@@ -9,7 +9,9 @@
   <sheets>
     <sheet name="Stavfel och språkbruk" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$9</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -17,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,6 +30,10 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <color rgb="000563C1"/>
+      <u val="single"/>
     </font>
   </fonts>
   <fills count="3">
@@ -55,11 +61,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -462,7 +469,242 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>GSQ23K</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>SQQ</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>`credtis` (en)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ23K</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>DITMG</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Utbildningsplaner</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>`mjukvarutestningsområdena` (sv)</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=DITMG</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>DITMG</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Utbildningsplaner</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>`mjukvarutestningsområdet` (sv)</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=DITMG</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>DSVPG</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Utbildningsplaner</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>`pär` (sv)</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=DSVPG</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>TTBRB</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Utbildningsplaner</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>`förutbildningen` (sv)</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TTBRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>TTBRB</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Utbildningsplaner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>`römsing` (sv)</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TTBRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>TTEKB</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Utbildningsplaner</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>`förutbildningen` (sv)</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TTEKB</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>TTEKB</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Utbildningsplaner</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>`römsing` (sv)</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TTEKB</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:E9"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/vault-dalarna-university/01 IIT/Analys/Stavfel och språkbruk.xlsx
+++ b/vault-dalarna-university/01 IIT/Analys/Stavfel och språkbruk.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Stavfel och språkbruk" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -472,27 +472,27 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>GSQ23K</t>
+          <t>DITMG</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SQQ</t>
+          <t>Utbildningsplaner</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>`credtis` (en)</t>
+          <t>`mjukvarutestningsområdena` (sv)</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ23K</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=DITMG</t>
         </is>
       </c>
     </row>
@@ -514,7 +514,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>`mjukvarutestningsområdena` (sv)</t>
+          <t>`mjukvarutestningsområdet` (sv)</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -526,7 +526,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>DITMG</t>
+          <t>DSVPG</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -541,19 +541,19 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>`mjukvarutestningsområdet` (sv)</t>
+          <t>`pär` (sv)</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=DITMG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=DSVPG</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>DSVPG</t>
+          <t>TTBRB</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -568,12 +568,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>`pär` (sv)</t>
+          <t>`förutbildningen` (sv)</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=DSVPG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TTBRB</t>
         </is>
       </c>
     </row>
@@ -595,7 +595,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>`förutbildningen` (sv)</t>
+          <t>`römsing` (sv)</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -607,7 +607,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>TTBRB</t>
+          <t>TTEKB</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -622,12 +622,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>`römsing` (sv)</t>
+          <t>`förutbildningen` (sv)</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TTBRB</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TTEKB</t>
         </is>
       </c>
     </row>
@@ -649,7 +649,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>`förutbildningen` (sv)</t>
+          <t>`römsing` (sv)</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -658,35 +658,8 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>TTEKB</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Utbildningsplaner</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>`römsing` (sv)</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TTEKB</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E9"/>
+  <autoFilter ref="A1:E8"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -702,8 +675,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId16"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/01 IIT/Analys/Stavfel och språkbruk.xlsx
+++ b/vault-dalarna-university/01 IIT/Analys/Stavfel och språkbruk.xlsx
@@ -9,9 +9,7 @@
   <sheets>
     <sheet name="Stavfel och språkbruk" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$8</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -19,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,10 +28,6 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-    </font>
-    <font>
-      <color rgb="000563C1"/>
-      <u val="single"/>
     </font>
   </fonts>
   <fills count="3">
@@ -61,12 +55,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -432,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -469,213 +462,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>DITMG</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Utbildningsplaner</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>`mjukvarutestningsområdena` (sv)</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=DITMG</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>DITMG</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Utbildningsplaner</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>`mjukvarutestningsområdet` (sv)</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=DITMG</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>DSVPG</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Utbildningsplaner</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>`pär` (sv)</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=DSVPG</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>TTBRB</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Utbildningsplaner</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>`förutbildningen` (sv)</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TTBRB</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>TTBRB</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Utbildningsplaner</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>`römsing` (sv)</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TTBRB</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>TTEKB</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Utbildningsplaner</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>`förutbildningen` (sv)</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TTEKB</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>TTEKB</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Utbildningsplaner</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Felstavning</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>`römsing` (sv)</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TTEKB</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E8"/>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId14"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/vault-dalarna-university/01 IIT/Analys/Stavfel och språkbruk.xlsx
+++ b/vault-dalarna-university/01 IIT/Analys/Stavfel och språkbruk.xlsx
@@ -9,7 +9,9 @@
   <sheets>
     <sheet name="Stavfel och språkbruk" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$8</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -17,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,6 +30,10 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <color rgb="000563C1"/>
+      <u val="single"/>
     </font>
   </fonts>
   <fills count="3">
@@ -55,11 +61,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -462,7 +469,213 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>DITMG</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Utbildningsplaner</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>`mjukvarutestningsområdena` (sv)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=DITMG</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>DITMG</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Utbildningsplaner</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>`mjukvarutestningsområdet` (sv)</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=DITMG</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>DSVPG</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Utbildningsplaner</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>`pär` (sv)</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=DSVPG</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>TTBRB</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Utbildningsplaner</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>`förutbildningen` (sv)</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TTBRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>TTBRB</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Utbildningsplaner</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>`römsing` (sv)</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TTBRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>TTEKB</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Utbildningsplaner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>`förutbildningen` (sv)</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TTEKB</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>TTEKB</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Utbildningsplaner</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>`römsing` (sv)</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TTEKB</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:E8"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/vault-dalarna-university/01 IIT/Analys/Stavfel och språkbruk.xlsx
+++ b/vault-dalarna-university/01 IIT/Analys/Stavfel och språkbruk.xlsx
@@ -9,7 +9,9 @@
   <sheets>
     <sheet name="Stavfel och språkbruk" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$10</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -17,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,6 +30,10 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <color rgb="000563C1"/>
+      <u val="single"/>
     </font>
   </fonts>
   <fills count="3">
@@ -55,11 +61,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -462,7 +469,271 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>FDA222R</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ANALYTIC</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>`contextualise` (en)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FDA222R</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>FDA222S</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ANALYTIC</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>`backpropagation` (en)</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FDA222S</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>FDA222S</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ANALYTIC</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>`feedforward` (en)</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FDA222S</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>FDA222S</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ANALYTIC</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>`rnns` (en)</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FDA222S</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>FEB222L</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ENERGIBM</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>`prosumers` (en)</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FEB222L</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>FEB222Q</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ENERGIBM</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>`contextualise` (en)</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FEB222Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>FEB222Q</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ENERGIBM</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>`transdisciplinary` (en)</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FEB222Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>FMI2222</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>MIKRODAT</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>`experiental` (en)</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FMI2222</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>FMI2224</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>MIKRODAT</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>`seperability` (en)</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FMI2224</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:E10"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId18"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/vault-dalarna-university/01 IIT/Analys/Stavfel och språkbruk.xlsx
+++ b/vault-dalarna-university/01 IIT/Analys/Stavfel och språkbruk.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Stavfel och språkbruk" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -472,12 +472,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>FDA222R</t>
+          <t>FMI2222</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ANALYTIC</t>
+          <t>MIKRODAT</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -487,24 +487,24 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>`contextualise` (en)</t>
+          <t>`experiental` (en)</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FDA222R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FMI2222</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>FDA222S</t>
+          <t>FMI2224</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ANALYTIC</t>
+          <t>MIKRODAT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -514,225 +514,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>`backpropagation` (en)</t>
+          <t>`seperability` (en)</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FDA222S</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>FDA222S</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>ANALYTIC</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>`feedforward` (en)</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FDA222S</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>FDA222S</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>ANALYTIC</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>`rnns` (en)</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FDA222S</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>FEB222L</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>ENERGIBM</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>`prosumers` (en)</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FEB222L</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>FEB222Q</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>ENERGIBM</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>`contextualise` (en)</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FEB222Q</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>FEB222Q</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>ENERGIBM</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>`transdisciplinary` (en)</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FEB222Q</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>FMI2222</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>MIKRODAT</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>`experiental` (en)</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FMI2222</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>FMI2224</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>MIKRODAT</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>`seperability` (en)</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FMI2224</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E10"/>
+  <autoFilter ref="A1:E3"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId18"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/01 IIT/Analys/Stavfel och språkbruk.xlsx
+++ b/vault-dalarna-university/01 IIT/Analys/Stavfel och språkbruk.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Stavfel och språkbruk" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -472,64 +472,209 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>FMI2222</t>
+          <t>DITMG</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MIKRODAT</t>
+          <t>Utbildningsplaner</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>`experiental` (en)</t>
+          <t>`mjukvarutestningsområdena` (sv)</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FMI2222</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=DITMG</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>FMI2224</t>
+          <t>DITMG</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MIKRODAT</t>
+          <t>Utbildningsplaner</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>`seperability` (en)</t>
+          <t>`mjukvarutestningsområdet` (sv)</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FMI2224</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=DITMG</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>DSVPG</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Utbildningsplaner</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>`pär` (sv)</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=DSVPG</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>TTBRB</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Utbildningsplaner</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>`förutbildningen` (sv)</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TTBRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>TTBRB</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Utbildningsplaner</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>`römsing` (sv)</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TTBRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>TTEKB</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Utbildningsplaner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>`förutbildningen` (sv)</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TTEKB</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>TTEKB</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Utbildningsplaner</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>`römsing` (sv)</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=TTEKB</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E3"/>
+  <autoFilter ref="A1:E8"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/01 IIT/Analys/Stavfel och språkbruk.xlsx
+++ b/vault-dalarna-university/01 IIT/Analys/Stavfel och språkbruk.xlsx
@@ -9,7 +9,9 @@
   <sheets>
     <sheet name="Stavfel och språkbruk" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$3</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -17,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,6 +30,10 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <color rgb="000563C1"/>
+      <u val="single"/>
     </font>
   </fonts>
   <fills count="3">
@@ -55,11 +61,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -462,7 +469,68 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>FMI2222</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>MIKRODAT</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>`experiental` (en)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FMI2222</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>FMI2224</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>MIKRODAT</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>`seperability` (en)</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FMI2224</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:E3"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/vault-dalarna-university/01 IIT/Analys/Stavfel och språkbruk.xlsx
+++ b/vault-dalarna-university/01 IIT/Analys/Stavfel och språkbruk.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Stavfel och språkbruk" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$E$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$G$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,14 +432,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="70" customWidth="1" min="4" max="4"/>
-    <col width="70" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="70" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -455,15 +457,25 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Fastställd</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Reviderad</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Problem</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Detalj</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Länk</t>
         </is>
@@ -482,15 +494,21 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>2019-10-03</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>Felstavning (en)</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>`experiental` (en)</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FMI2222</t>
         </is>
@@ -509,27 +527,33 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>2019-10-29</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>Felstavning (en)</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>`seperability` (en)</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FMI2224</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E3"/>
+  <autoFilter ref="A1:G3"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/01 IIT/Analys/Stavfel och språkbruk.xlsx
+++ b/vault-dalarna-university/01 IIT/Analys/Stavfel och språkbruk.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Stavfel och språkbruk" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$G$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$G$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -484,76 +484,718 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>FMI2222</t>
+          <t>BY3005</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MIKRODAT</t>
+          <t>BYA</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2019-10-03</t>
+          <t>2017-12-14</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Felstavning (en)</t>
+          <t>Felstavning</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>`experiental` (en)</t>
+          <t>`sät` (sv)</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FMI2222</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BY3005</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>FMI2224</t>
+          <t>GBY2GR</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MIKRODAT</t>
+          <t>BYA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2019-10-29</t>
+          <t>2020-04-30</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>`bedömni` (sv)</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2GR</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>GBY2NG</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>BYA</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2021-02-18</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>`genomförand` (sv)</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2NG</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>GBY2XF</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>BYA</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2022-09-05</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>`sammanvägni` (sv)</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBY2XF</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>GIK2XJ</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>IKA</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2022-09-06</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>`helhetsbedö` (sv)</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2XJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>GIK2XZ</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>IKA</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2022-09-27</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>`öve` (sv)</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIK2XZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>MA0011</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>MAA</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2013-12-12</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>`godkän` (sv)</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MA0011</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>MA0013</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>MAA</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2014-01-30</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>`godkän` (sv)</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MA0013</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>AMD238</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>MDI</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2019-06-19</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>`problemområ` (sv)</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMD238</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>GMD2BH</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>MDI</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2019-08-29</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2019-09-19</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>`inlämnin` (sv)</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2BH</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>GMD2TV</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>MDI</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2021-12-22</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2022-05-23</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>`nätuppkop` (sv)</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMD2TV</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>MD1103</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>MDI</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2015-10-01</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2021-12-03</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>`inlämningsupp` (sv)</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MD1103</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>FMI2222</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>MIKRODAT</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2019-10-03</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>Felstavning (en)</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>`experiental` (en)</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FMI2222</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>FMI2224</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>MIKRODAT</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2019-10-29</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
         <is>
           <t>`seperability` (en)</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FMI2224</t>
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>AEG26X</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2021-05-20</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>`inlämningsuppgi` (sv)</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEG26X</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>EG1012</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2017-10-12</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>`strömningsl` (sv)</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG1012</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>EG3020</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2017-12-14</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>`överb` (sv)</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EG3020</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>GSQ25J</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>SQQ</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2018-10-29</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>`inlämningsuppgifte` (sv)</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ25J</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>GSQ2LA</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>SQQ</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2020-12-17</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>`sät` (sv)</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2LA</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>GSQ2Y2</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>SQQ</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2022-09-27</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Felstavning</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>`genomgånge` (sv)</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSQ2Y2</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G3"/>
+  <autoFilter ref="A1:G21"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A21" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId40"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/01 IIT/Analys/Stavfel och språkbruk.xlsx
+++ b/vault-dalarna-university/01 IIT/Analys/Stavfel och språkbruk.xlsx
@@ -9,9 +9,7 @@
   <sheets>
     <sheet name="Stavfel och språkbruk" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$G$3</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -19,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,10 +28,6 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-    </font>
-    <font>
-      <color rgb="000563C1"/>
-      <u val="single"/>
     </font>
   </fonts>
   <fills count="3">
@@ -61,12 +55,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -432,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -481,80 +474,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>FMI2222</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>MIKRODAT</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2019-10-03</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>`experiental` (en)</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FMI2222</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>FMI2224</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>MIKRODAT</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2019-10-29</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Felstavning (en)</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>`seperability` (en)</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FMI2224</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:G3"/>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId4"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/vault-dalarna-university/01 IIT/Analys/Stavfel och språkbruk.xlsx
+++ b/vault-dalarna-university/01 IIT/Analys/Stavfel och språkbruk.xlsx
@@ -9,7 +9,9 @@
   <sheets>
     <sheet name="Stavfel och språkbruk" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$G$5</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -17,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,6 +30,10 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <color rgb="000563C1"/>
+      <u val="single"/>
     </font>
   </fonts>
   <fills count="3">
@@ -55,11 +61,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -474,7 +481,150 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>GIE3JS</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>IEA</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>`understandingwithin` (en)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIE3JS</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>GMT3JR</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>MTA</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>`mechanicsthe` (en)</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT3JR</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>GMT3JR</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>MTA</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>`vapours` (en)</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT3JR</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>GMT3JV</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>MTA</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>`assessmen` (en)</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMT3JV</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:G5"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/vault-dalarna-university/01 IIT/Analys/Stavfel och språkbruk.xlsx
+++ b/vault-dalarna-university/01 IIT/Analys/Stavfel och språkbruk.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Stavfel och språkbruk" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$G$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stavfel och språkbruk'!$A$1:$G$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -613,8 +613,41 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>GEG3K9</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>MÖY</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Felstavning (en)</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>`thebasic` (en)</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEG3K9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G5"/>
+  <autoFilter ref="A1:G6"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
@@ -624,6 +657,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
